--- a/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13219</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480863</t>
+          <t>480845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491251</t>
+          <t>491203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449453</t>
+          <t>450120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461968</t>
+          <t>462007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>934688</t>
+          <t>935504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>950916</t>
+          <t>951180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710258</t>
+          <t>711599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>726559</t>
+          <t>725915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>603209</t>
+          <t>602716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>618133</t>
+          <t>618218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1320475</t>
+          <t>1319182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1342218</t>
+          <t>1341236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32756</t>
+          <t>34079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47037</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70512</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605912</t>
+          <t>604589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625514</t>
+          <t>625443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642707</t>
+          <t>642916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667937</t>
+          <t>667241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1257900</t>
+          <t>1256852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288697</t>
+          <t>1288828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39899</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54123</t>
+          <t>53210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499363</t>
+          <t>498396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512989</t>
+          <t>512947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475743</t>
+          <t>475375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496836</t>
+          <t>496486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>980666</t>
+          <t>981579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1005311</t>
+          <t>1006172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>52422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361282</t>
+          <t>361164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377493</t>
+          <t>377620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371126</t>
+          <t>370503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389848</t>
+          <t>389059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>739905</t>
+          <t>738274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762544</t>
+          <t>762389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>34535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26730</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48848</t>
+          <t>49526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272364</t>
+          <t>273080</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>285583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307793</t>
+          <t>308399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326346</t>
+          <t>327080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586669</t>
+          <t>585991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>608787</t>
+          <t>609332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>35349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42605</t>
+          <t>43948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195425</t>
+          <t>196506</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206244</t>
+          <t>206405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298982</t>
+          <t>298559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318739</t>
+          <t>318826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>501186</t>
+          <t>499843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>522690</t>
+          <t>521941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129417</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181201</t>
+          <t>182661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>216538</t>
+          <t>217358</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278899</t>
+          <t>277457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3165223</t>
+          <t>3165544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3203898</t>
+          <t>3202917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3197996</t>
+          <t>3196536</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3249780</t>
+          <t>3246502</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6376842</t>
+          <t>6378284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6439203</t>
+          <t>6438383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14048</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442858</t>
+          <t>443601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452134</t>
+          <t>452304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416182</t>
+          <t>416220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427199</t>
+          <t>427281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863202</t>
+          <t>863716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>877657</t>
+          <t>877622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29598</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670380</t>
+          <t>670685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682496</t>
+          <t>682445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>580657</t>
+          <t>581142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>598882</t>
+          <t>598786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1257368</t>
+          <t>1257356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1277677</t>
+          <t>1278212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>45176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47516</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50519</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86584</t>
+          <t>83413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637255</t>
+          <t>636687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661312</t>
+          <t>660399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>663334</t>
+          <t>662571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687320</t>
+          <t>687502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306128</t>
+          <t>1309299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1342193</t>
+          <t>1342715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>45537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>67593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>583587</t>
+          <t>583866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>604088</t>
+          <t>603835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>569645</t>
+          <t>570662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593002</t>
+          <t>593101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161480</t>
+          <t>1163223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191920</t>
+          <t>1192891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27960</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52859</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407371</t>
+          <t>406495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421135</t>
+          <t>421552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>411841</t>
+          <t>411379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>431575</t>
+          <t>430945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>824370</t>
+          <t>824394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>849269</t>
+          <t>848343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>22230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>35336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61048</t>
+          <t>60918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287690</t>
+          <t>287556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>302126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309063</t>
+          <t>309198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329802</t>
+          <t>330456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602734</t>
+          <t>602864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628843</t>
+          <t>628446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>34774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50349</t>
+          <t>52480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228339</t>
+          <t>228186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243622</t>
+          <t>243480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>353282</t>
+          <t>354205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>372851</t>
+          <t>373548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>588481</t>
+          <t>586350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>613155</t>
+          <t>612273</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152205</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207429</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>247516</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314833</t>
+          <t>316364</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3301223</t>
+          <t>3297367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3341826</t>
+          <t>3339546</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3350880</t>
+          <t>3354127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3406104</t>
+          <t>3407663</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6670255</t>
+          <t>6668724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6737572</t>
+          <t>6734667</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400804</t>
+          <t>400466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413992</t>
+          <t>413757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>370085</t>
+          <t>369822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386086</t>
+          <t>386662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>777202</t>
+          <t>776512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>797134</t>
+          <t>797169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>22925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44722</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>567117</t>
+          <t>568405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>582664</t>
+          <t>582782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>533898</t>
+          <t>534397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>550678</t>
+          <t>551572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1109318</t>
+          <t>1107572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1130743</t>
+          <t>1131115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>36893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39268</t>
+          <t>40489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>67109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>63756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95022</t>
+          <t>94382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633244</t>
+          <t>632204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652838</t>
+          <t>652687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>595758</t>
+          <t>594277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>622118</t>
+          <t>620897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1235461</t>
+          <t>1236101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1268502</t>
+          <t>1266727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>24280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>46818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>62956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98864</t>
+          <t>98694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94396</t>
+          <t>93266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135580</t>
+          <t>135048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598729</t>
+          <t>599230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621833</t>
+          <t>621768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550213</t>
+          <t>550383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>586326</t>
+          <t>586121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1159545</t>
+          <t>1160077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1200729</t>
+          <t>1201859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75868</t>
+          <t>75937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111710</t>
+          <t>110922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105491</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148324</t>
+          <t>150586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430105</t>
+          <t>429912</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454002</t>
+          <t>454606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>385139</t>
+          <t>385927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>420981</t>
+          <t>420912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826443</t>
+          <t>824181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869276</t>
+          <t>868308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48395</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>77703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60933</t>
+          <t>59900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94680</t>
+          <t>93227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311450</t>
+          <t>312377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326382</t>
+          <t>326516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300311</t>
+          <t>300059</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329367</t>
+          <t>330004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>617412</t>
+          <t>618865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651159</t>
+          <t>652192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>51957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85962</t>
+          <t>86165</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72273</t>
+          <t>71352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110080</t>
+          <t>110684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225559</t>
+          <t>225190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>242193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>314207</t>
+          <t>314004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347650</t>
+          <t>348212</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>547087</t>
+          <t>546483</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>584894</t>
+          <t>585815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>129217</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179186</t>
+          <t>177646</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>354888</t>
+          <t>351692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430916</t>
+          <t>431385</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495007</t>
+          <t>502869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>591483</t>
+          <t>592778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3215164</t>
+          <t>3216704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3264188</t>
+          <t>3265133</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3113626</t>
+          <t>3113157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3189654</t>
+          <t>3192850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6347409</t>
+          <t>6346114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6443885</t>
+          <t>6436023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379963</t>
+          <t>377934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294929</t>
+          <t>293860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311332</t>
+          <t>311028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681796</t>
+          <t>681573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707725</t>
+          <t>707912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>39695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402150</t>
+          <t>403371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419563</t>
+          <t>419740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485730</t>
+          <t>487466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504760</t>
+          <t>505048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>896549</t>
+          <t>895945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920904</t>
+          <t>920758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46024</t>
+          <t>46785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506268</t>
+          <t>506465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525161</t>
+          <t>525476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568475</t>
+          <t>567293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581784</t>
+          <t>581743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1082316</t>
+          <t>1081555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1104026</t>
+          <t>1104784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46080</t>
+          <t>45411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84679</t>
+          <t>87255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839660</t>
+          <t>842344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876655</t>
+          <t>877035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666801</t>
+          <t>667470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686598</t>
+          <t>686057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1515988</t>
+          <t>1513412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1564640</t>
+          <t>1560041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32470</t>
+          <t>32624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>43637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>45797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69708</t>
+          <t>70744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>528764</t>
+          <t>528610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546889</t>
+          <t>546455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>504179</t>
+          <t>504268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520606</t>
+          <t>520558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1039431</t>
+          <t>1038395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1062938</t>
+          <t>1063342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35240</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>449430</t>
+          <t>436522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44250</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>575514</t>
+          <t>578649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349509</t>
+          <t>348939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360940</t>
+          <t>360580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158938</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>573128</t>
+          <t>573103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>401019</t>
+          <t>397884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>932283</t>
+          <t>932032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30504</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48407</t>
+          <t>47746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>260545</t>
+          <t>262206</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273429</t>
+          <t>274037</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>393772</t>
+          <t>393931</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>407123</t>
+          <t>407421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>660183</t>
+          <t>660844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>678086</t>
+          <t>679022</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88845</t>
+          <t>82858</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>161276</t>
+          <t>161437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>988032</t>
+          <t>979354</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>271451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1189282</t>
+          <t>1132535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3318077</t>
+          <t>3322540</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3370972</t>
+          <t>3376959</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2724248</t>
+          <t>2732926</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3551004</t>
+          <t>3550843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5982815</t>
+          <t>6039562</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6903784</t>
+          <t>6900646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480845</t>
+          <t>479849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491203</t>
+          <t>491133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>450120</t>
+          <t>449402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>462007</t>
+          <t>461988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>935504</t>
+          <t>935091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>951180</t>
+          <t>951090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>711599</t>
+          <t>711816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>725915</t>
+          <t>726529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>602716</t>
+          <t>602623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>618218</t>
+          <t>618321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1319182</t>
+          <t>1319771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1341236</t>
+          <t>1341442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>46845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39584</t>
+          <t>40336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604589</t>
+          <t>605759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625443</t>
+          <t>625071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642916</t>
+          <t>642899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667241</t>
+          <t>667188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256852</t>
+          <t>1257311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288828</t>
+          <t>1288076</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40267</t>
+          <t>40457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>53295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498396</t>
+          <t>499775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512947</t>
+          <t>513045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475375</t>
+          <t>475185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496486</t>
+          <t>496000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>981579</t>
+          <t>981494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1006172</t>
+          <t>1005422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>32394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>28314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52422</t>
+          <t>52777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361164</t>
+          <t>361508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377620</t>
+          <t>377155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370503</t>
+          <t>371592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389059</t>
+          <t>389419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>738274</t>
+          <t>737919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762389</t>
+          <t>762382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>33895</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49526</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273080</t>
+          <t>273246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285583</t>
+          <t>285806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308399</t>
+          <t>309039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>327080</t>
+          <t>326309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>585991</t>
+          <t>586388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609332</t>
+          <t>609222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15082</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43948</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196506</t>
+          <t>196115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206405</t>
+          <t>206411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298559</t>
+          <t>300044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318826</t>
+          <t>318885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>499843</t>
+          <t>498931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>521941</t>
+          <t>522133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73626</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110999</t>
+          <t>109749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132695</t>
+          <t>129995</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>181669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>217358</t>
+          <t>215957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277457</t>
+          <t>278037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3165544</t>
+          <t>3166794</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3202917</t>
+          <t>3202364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3196536</t>
+          <t>3197528</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3246502</t>
+          <t>3249202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6378284</t>
+          <t>6377704</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6438383</t>
+          <t>6439784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443601</t>
+          <t>441948</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452304</t>
+          <t>452052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416220</t>
+          <t>417120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427281</t>
+          <t>427344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863716</t>
+          <t>863452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>877622</t>
+          <t>877551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29113</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>40398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670685</t>
+          <t>670473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682445</t>
+          <t>682466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581142</t>
+          <t>581570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>598786</t>
+          <t>598669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1257356</t>
+          <t>1256944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1278212</t>
+          <t>1277891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45176</t>
+          <t>46571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49997</t>
+          <t>51148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83413</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636687</t>
+          <t>635292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660399</t>
+          <t>659943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662571</t>
+          <t>662587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687502</t>
+          <t>687913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309299</t>
+          <t>1310155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1342715</t>
+          <t>1341564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30751</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45537</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67593</t>
+          <t>66793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>583866</t>
+          <t>583589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>603835</t>
+          <t>604021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570662</t>
+          <t>569397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593101</t>
+          <t>592935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1163223</t>
+          <t>1164023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192891</t>
+          <t>1192608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>27536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406495</t>
+          <t>405921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421552</t>
+          <t>421401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>411379</t>
+          <t>409817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430945</t>
+          <t>430968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>824394</t>
+          <t>825986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>848343</t>
+          <t>849693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>22261</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35336</t>
+          <t>35611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287556</t>
+          <t>287525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302126</t>
+          <t>302120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309198</t>
+          <t>309394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330456</t>
+          <t>330590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602864</t>
+          <t>602725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628446</t>
+          <t>628171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52480</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228186</t>
+          <t>227587</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243480</t>
+          <t>243767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>354205</t>
+          <t>352783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>373548</t>
+          <t>372908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>586350</t>
+          <t>587589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>612273</t>
+          <t>612894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87233</t>
+          <t>84969</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129412</t>
+          <t>127591</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150646</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204182</t>
+          <t>205236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>250421</t>
+          <t>246593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>316364</t>
+          <t>316238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3297367</t>
+          <t>3299188</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3339546</t>
+          <t>3341810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3354127</t>
+          <t>3353073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3407663</t>
+          <t>3405010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6668724</t>
+          <t>6668850</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6734667</t>
+          <t>6738495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38706</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400466</t>
+          <t>399630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413757</t>
+          <t>413593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>370529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386662</t>
+          <t>386192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>776512</t>
+          <t>777233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>797169</t>
+          <t>797212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>30940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,47 +7084,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>33127</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>24415</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>33127</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>22925</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>46468</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>568405</t>
+          <t>568072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>582782</t>
+          <t>583261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>534397</t>
+          <t>532604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>551572</t>
+          <t>551335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,47 +7197,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1120913</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1108040</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1129625</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,01%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,88%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1120913</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1107572</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1131115</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67109</t>
+          <t>66604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>62384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94382</t>
+          <t>95460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632204</t>
+          <t>632585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652687</t>
+          <t>652374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594277</t>
+          <t>594782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>620897</t>
+          <t>620610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236101</t>
+          <t>1235023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1266727</t>
+          <t>1268099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46818</t>
+          <t>47228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62956</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98694</t>
+          <t>98219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93266</t>
+          <t>93315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135048</t>
+          <t>135103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599230</t>
+          <t>598820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621768</t>
+          <t>621658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550383</t>
+          <t>550858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>586121</t>
+          <t>585188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160077</t>
+          <t>1160022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1201859</t>
+          <t>1201810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48006</t>
+          <t>46980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75937</t>
+          <t>75579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110922</t>
+          <t>110266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>108345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150586</t>
+          <t>150851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429912</t>
+          <t>430938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454606</t>
+          <t>453948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>385927</t>
+          <t>386583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>420912</t>
+          <t>421270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>824181</t>
+          <t>823916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868308</t>
+          <t>866422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47758</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77703</t>
+          <t>77495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59900</t>
+          <t>58563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93227</t>
+          <t>93440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312377</t>
+          <t>312465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326516</t>
+          <t>326349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300059</t>
+          <t>300267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330004</t>
+          <t>329979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618865</t>
+          <t>618652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>652192</t>
+          <t>653529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51957</t>
+          <t>52268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86165</t>
+          <t>87169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71352</t>
+          <t>71398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110684</t>
+          <t>109512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225190</t>
+          <t>226224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242193</t>
+          <t>242754</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>314004</t>
+          <t>313000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348212</t>
+          <t>347901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546483</t>
+          <t>547655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>585815</t>
+          <t>585769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129217</t>
+          <t>130715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177646</t>
+          <t>179509</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351692</t>
+          <t>352922</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>431385</t>
+          <t>429414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>502869</t>
+          <t>500698</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>592778</t>
+          <t>595868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3216704</t>
+          <t>3214841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3265133</t>
+          <t>3263635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3113157</t>
+          <t>3115128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3192850</t>
+          <t>3191620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6346114</t>
+          <t>6343024</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6436023</t>
+          <t>6438194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31614</t>
+          <t>28064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>393801</t>
+          <t>402626</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377934</t>
+          <t>389960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>305366</t>
+          <t>354440</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293860</t>
+          <t>343601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311028</t>
+          <t>360295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>699167</t>
+          <t>757066</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681573</t>
+          <t>742241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707912</t>
+          <t>765087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>25742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24627</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>29588</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>46449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>413546</t>
+          <t>465020</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403371</t>
+          <t>451148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419740</t>
+          <t>471950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>497514</t>
+          <t>484015</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487466</t>
+          <t>471396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505048</t>
+          <t>491906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>911059</t>
+          <t>949035</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>895945</t>
+          <t>932174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920758</t>
+          <t>960190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46785</t>
+          <t>52193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518003</t>
+          <t>601612</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506465</t>
+          <t>589293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525476</t>
+          <t>609303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>576218</t>
+          <t>604124</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>567293</t>
+          <t>595759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581743</t>
+          <t>611056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1094222</t>
+          <t>1205735</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1081555</t>
+          <t>1191836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1104784</t>
+          <t>1216286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>42694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>39392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45411</t>
+          <t>50359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65354</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87255</t>
+          <t>86264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>857890</t>
+          <t>669958</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842344</t>
+          <t>657923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877035</t>
+          <t>680273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677422</t>
+          <t>697494</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667470</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686057</t>
+          <t>706117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1535313</t>
+          <t>1367452</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1513412</t>
+          <t>1351240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1560041</t>
+          <t>1381897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32624</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27347</t>
+          <t>31447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43637</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>57261</t>
+          <t>64527</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45797</t>
+          <t>51765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70744</t>
+          <t>79572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>538998</t>
+          <t>585026</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>528610</t>
+          <t>573403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546455</t>
+          <t>593106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>512881</t>
+          <t>568648</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>504268</t>
+          <t>558551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520558</t>
+          <t>577408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1051878</t>
+          <t>1153675</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1038395</t>
+          <t>1138630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1063342</t>
+          <t>1166437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,22 +11380,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>230594</t>
+          <t>28564</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35265</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>436522</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>242950</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>578649</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -11493,27 +11493,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>355809</t>
+          <t>392832</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348939</t>
+          <t>384992</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360580</t>
+          <t>398682</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>377774</t>
+          <t>410602</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171846</t>
+          <t>402135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>573103</t>
+          <t>417707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>733583</t>
+          <t>803434</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>397884</t>
+          <t>792481</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>932032</t>
+          <t>812780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>53916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>268647</t>
+          <t>293514</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>284973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274037</t>
+          <t>299060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>401388</t>
+          <t>437903</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>393931</t>
+          <t>429955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>407421</t>
+          <t>444664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>670035</t>
+          <t>731418</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>660844</t>
+          <t>720891</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>679022</t>
+          <t>740729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>113122</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82858</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137277</t>
+          <t>148500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>179728</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>161437</t>
+          <t>157768</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>979354</t>
+          <t>204755</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>476840</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>271451</t>
+          <t>272941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1132535</t>
+          <t>336245</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3346695</t>
+          <t>3410588</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3322540</t>
+          <t>3384262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3376959</t>
+          <t>3431064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3348563</t>
+          <t>3557226</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2732926</t>
+          <t>3532199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3550843</t>
+          <t>3579186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6695257</t>
+          <t>6967814</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6039562</t>
+          <t>6933471</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6900646</t>
+          <t>6996775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
